--- a/AAII_Financials/Quarterly/SNOW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNOW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>SNOW</t>
   </si>
@@ -656,429 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1546800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1391000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1284000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1212900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1145000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1042100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>986800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>942100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>868800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>828700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>774700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>734200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>674000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>623600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>589000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>557000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>497200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>422400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>383800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>334400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>272200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>228900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>190500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>159600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>133100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>108800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>87700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>73000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>60300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>43700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>36700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>510100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>464500</v>
+      </c>
+      <c r="F9" s="3">
         <v>426300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>390900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>371800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>348800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>333200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>320900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>288100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>272500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>241800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>228900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>218400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>209400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>205700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>190700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>173200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>147900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>134200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>120800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>106100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>97300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>82900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>66700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>50400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>42600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>34500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>29500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>28500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>24000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>20400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>13800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1036700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>926500</v>
+      </c>
+      <c r="F10" s="3">
         <v>857700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>822000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>773200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>693300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>653600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>621200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>580700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>556200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>532900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>505200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>455600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>414200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>383300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>366300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>324000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>274500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>249600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>213600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>166100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>131600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>107600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>92900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>82700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>66200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>53200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>43500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>31800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>19700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>16300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1137,111 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>567500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>534900</v>
+      </c>
+      <c r="F12" s="3">
         <v>511000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>494000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>492000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>472400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>492500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>442400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>437700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>410800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>364500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>332100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>314000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>270300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>242100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>211400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>183700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>150800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>123100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>115900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>118100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>109800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>94000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>74100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>36500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>33300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>29700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>27700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>26200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>21600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>27600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,65 +1335,71 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-84200</v>
+        <v>-34800</v>
       </c>
       <c r="E14" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F14" s="3">
+        <v>24400</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>5600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>136200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-4400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>8600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>6500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>20700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-45700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-5300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>9500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>8900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>26700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1370,11 +1409,11 @@
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1397,53 +1436,59 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F15" s="3">
         <v>39500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>39500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>37800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>32000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>33100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>31800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>31800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>29300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>28300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>27600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>25400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>19700</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1710800</v>
+        <v>1809800</v>
       </c>
       <c r="E17" s="3">
+        <v>1699400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1602200</v>
+      </c>
+      <c r="G17" s="3">
         <v>1542400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1485200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1382800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1373400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1307600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1224100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1177300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1050200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>994800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>959400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>889700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>832800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>770500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>731500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>611100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>535800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>491700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>472300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>434500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>390900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>329100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>210800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>205200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>172800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>163100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>155900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>131000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>108400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>67700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-426800</v>
+        <v>-263000</v>
       </c>
       <c r="E18" s="3">
+        <v>-308400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-318200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-329500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-340300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-340800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-386700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-365500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-355300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-348600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-275500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-260600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-285400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-266100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-243800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-213500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-234300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-188700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-152000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-157300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-200100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-205600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-200400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-169500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-96400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-85100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-90100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-95600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-87300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-71700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-39000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,198 +1814,212 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>36600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>16100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>15400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>21400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>3600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>10900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>2100</v>
       </c>
       <c r="AC20" s="3">
         <v>2500</v>
       </c>
       <c r="AD20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AF20" s="3">
         <v>2700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>3300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>4200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-387000</v>
+        <v>-210000</v>
       </c>
       <c r="E21" s="3">
+        <v>-257900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-278400</v>
+      </c>
+      <c r="G21" s="3">
         <v>-291600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-301800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-307100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-355600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-333500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-324900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-319900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-245400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-235400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-261200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-246600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-187400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-179700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-202800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-182500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-124700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-148200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-183800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-198800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-194400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-165600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-74900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-92400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-83400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1960,14 +2039,14 @@
         <v>2100</v>
       </c>
       <c r="I22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1980,11 +2059,11 @@
       <c r="O22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2034,198 +2113,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-188300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-296700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-301900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-287900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-297900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-424200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-330100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-326000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-314000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-315100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-174200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-211300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-231000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-232700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-207100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-197400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-219000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-192500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-130600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-153700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-189200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-203500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-197600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-168500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-77100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-93900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-87700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-92900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-67600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-37100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F24" s="3">
         <v>7700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>3700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>5700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-6600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>3800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-26700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-191700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-295600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-309600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-291600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-297900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-430000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-325700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-327900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-317800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-317800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-169900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-214700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-227300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-226100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-207500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-201400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-222800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-165800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-132200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-154900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-189700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-203200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-198900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-168900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-77600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-83300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-88100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-93400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-83800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-67900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-191700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-295600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-309600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-294000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-298000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-430100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-327500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-324300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-316900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-317000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-169400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-214300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-226900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-225600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-207200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-200900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-222800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-165800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-132200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-154900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-189700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-203200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-198900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-168900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-77600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-83300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-88100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-93400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-83800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-67900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +3022,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-16100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-15400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-21400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-3600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-10900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-2100</v>
       </c>
       <c r="AC32" s="3">
         <v>-2500</v>
       </c>
       <c r="AD32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-191700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-295600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-309600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-294000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-298000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-430100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-327500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-324300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-316900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-317000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-169400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-214300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-226900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-225600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-207200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-200900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-222800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-165800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-132200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-154900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-189700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-203200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-198900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-168900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-77600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-83300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-88100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-93400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-83800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-67900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-191700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-295600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-309600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-294000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-298000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-430100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-327500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-324300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-316900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-317000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-169400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-214300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-226900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-225600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-207200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-200900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-222800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-165800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-132200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-154900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-189700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-203200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-198900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-168900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-77600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-83300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-88100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-93400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-83800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-67900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,89 +3610,91 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1707200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2084700</v>
+      </c>
+      <c r="F41" s="3">
         <v>2828200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1941700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1880700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2243100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2628800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2148900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1282000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1330400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1762700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>982200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>755200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>653000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>939900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>819000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>906700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1063400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1085700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>935200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>698500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>644700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>820200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3939900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>138900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>437600</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3534,89 +3707,95 @@
       <c r="AG41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>637500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>870300</v>
+      </c>
+      <c r="F42" s="3">
         <v>1201500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1411400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1706000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1667600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>2008900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2008100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1948500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2200900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2083500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2566400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2996900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3292500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3068000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>3123900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>3046500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>2751700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2766400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2955600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>3436900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>3285800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>3087900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>814100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>452000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>372500</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3629,89 +3808,95 @@
       <c r="AG42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>745800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>601000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1320600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>960200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>670900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>552900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>946400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>618900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>452800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>368100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>951100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>534400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>432700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>375900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>715800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>394100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>305000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>277600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>545600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>254200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>237500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>166300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>294000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>169000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>151200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>96100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3724,8 +3909,14 @@
       <c r="AG43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3765,11 +3956,11 @@
       <c r="O44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3819,89 +4010,95 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>222100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>215100</v>
+      </c>
+      <c r="F45" s="3">
         <v>215800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>172500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>129900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>104200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>99200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>89800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>86900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>85400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>86100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>74600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>72000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>69200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>261000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>222000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>245600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>249100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>200900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>163200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>135200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>124600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>98600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>63700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>51400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>60300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3914,89 +4111,95 @@
       <c r="AG45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3493800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3977100</v>
+      </c>
+      <c r="F46" s="3">
         <v>5742600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4623500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4596100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4786000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5869400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4984100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3898100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4143300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5039300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4312300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4405000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4569500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4984700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4558900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4503700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4341700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4598600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4308300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4508100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4221300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4300700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4986800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>793400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>966600</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4009,89 +4212,95 @@
       <c r="AG46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2354700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1786000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1135600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1397300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1363900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1287300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>957700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1189000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1013400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1146500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1150700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1172900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1326600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1293500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1276000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1142500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1086700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1212400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1256200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1211900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>956000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1177700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1165300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>347400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>295900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>118900</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4104,89 +4313,95 @@
       <c r="AG47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>444300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>461800</v>
+      </c>
+      <c r="F48" s="3">
         <v>447000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>427000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>439300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>436300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>530900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>422200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>413600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>398400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>436400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>424200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>420000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>379000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>392100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>380700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>352300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>307600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>295400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>278400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>258600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>259100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>255800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>242900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>229800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>222500</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4199,89 +4414,95 @@
       <c r="AG48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2114300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2048900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1517800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1525100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1566600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1426500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1459500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1396000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1394200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1393800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1370500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1160600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1156400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>994500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>843400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>845300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>674900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>684500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>45600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>34600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>36500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>38200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>24500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>23300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>24100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>17400</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,89 +4717,95 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>58500</v>
+      </c>
+      <c r="F52" s="3">
         <v>47700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>47900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>43600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>38600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>32500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>33700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>47100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>36100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>39400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>44000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>55500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>67500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>226200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>228400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>446500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>476600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>453800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>330300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>273100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>232600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>175500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>112500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>93900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>90700</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4579,8 +4818,14 @@
       <c r="AG52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,89 +4919,95 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8690500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8554300</v>
+      </c>
+      <c r="F54" s="3">
         <v>9132500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8230200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8196700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8157400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9033900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>8202300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6943900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7298000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8223400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>7264400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>7509800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>7446800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>7722300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7155700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>7064100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>7022700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6649700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6163500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6032400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5929000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5921700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5712900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1437200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1416200</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4769,8 +5020,14 @@
       <c r="AG54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,89 +5098,91 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>55100</v>
+      </c>
+      <c r="F57" s="3">
         <v>145600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>193700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>166800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>155300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>169800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>148900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>134500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>64200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>51700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>75500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>41200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>22200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>54100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>55700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>48900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>42200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>31000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>27100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>16800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>10900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>19000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>19600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4934,53 +5195,59 @@
       <c r="AG57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>55800</v>
+      </c>
+      <c r="F58" s="3">
         <v>49600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>40200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>38100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>37100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>35900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>38300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>32800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>30900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>33900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>33300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>33800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>29200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5029,89 +5296,95 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2745800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3029200</v>
+      </c>
+      <c r="F59" s="3">
         <v>3537600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2586500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2481700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2449900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2696800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2091400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1943700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2013100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2302500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1671200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1624800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1670900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1939400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1423300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1352500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1321500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1366100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>931600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>858900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>766100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>770300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>528100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>469900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>400700</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5124,89 +5397,95 @@
       <c r="AG59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3721500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3777300</v>
+      </c>
+      <c r="F60" s="3">
         <v>4421700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3383300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3096100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3030500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3301200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2647300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2464700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2428800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2731200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2032700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1913300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1887500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1993500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1479000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1401400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1363700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1397100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>958700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>875700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>777000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>789300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>547700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>477700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>406300</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5219,53 +5498,59 @@
       <c r="AG60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2704000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2716300</v>
+      </c>
+      <c r="F61" s="3">
         <v>2691500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2645400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2654200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2650700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2649300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2557300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>280000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>247500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>254000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>253000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>263000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>225700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5314,89 +5599,95 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>95300</v>
+      </c>
+      <c r="F62" s="3">
         <v>80700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>57700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>55300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>47600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>61300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>51300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>49400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>39300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>33100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>25800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>22800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>21400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>260200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>253400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>236400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>201000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>203600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>198100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>191700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>193700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>196000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>197400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>195900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>198900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5409,8 +5700,14 @@
       <c r="AG62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,89 +6003,95 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6540800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6614500</v>
+      </c>
+      <c r="F66" s="3">
         <v>7208400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6097300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5817100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5742600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6027300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5267800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2806300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2730300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3032800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2323600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2211600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2148800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2265900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1744900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1637800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1564700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1600700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1156800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1067500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>970700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>985300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>745100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>673600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>605200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5789,8 +6104,14 @@
       <c r="AG66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6086,17 +6421,17 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>1415000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>1415000</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,89 +6545,95 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10281500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-10089800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-9494200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-9034700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-8512300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-8214500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-7293600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-6970500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-5625800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-4908900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-4075600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3906300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-3292000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-3065100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-2716100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-2508900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-2308000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-2085200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1919400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-1787200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1632400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-1442600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-1239400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-1040500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-871600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-794000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6299,8 +6646,14 @@
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,89 +6949,95 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2149700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1939700</v>
+      </c>
+      <c r="F76" s="3">
         <v>1924100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2132900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2372600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2408000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2999900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2929400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4129000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4558200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5180300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4929900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5286900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5286200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5456400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5410800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5426300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5458000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5049000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5006700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4965000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4958300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4936500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4967800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-651400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-604000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6679,8 +7050,14 @@
       <c r="AG76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-191700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-295600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-309600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-294000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-298000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-430100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-327500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-324300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-316900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-317000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-169400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-214300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-226900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-225600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-207200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-200900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-222800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-165800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-132200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-154900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-189700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-203200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-198900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-168900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-77600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-83300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-88100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-93400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-83800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-67900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,89 +7399,91 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>7700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>7900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>19700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>17700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>16200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>9900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>5900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>5500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>5400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>4700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>3200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>2200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1500</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>16</v>
       </c>
@@ -7099,8 +7496,14 @@
       <c r="AG83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,89 +8001,95 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>243200</v>
+      </c>
+      <c r="F89" s="3">
         <v>781200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>137500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>74900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>228400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>432700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>101700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>69900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>355500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>344600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>120900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>83200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>299400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>217300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>79300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>64400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>184600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>78900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>15500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-6100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>21900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>19600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-19800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-38700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7669,8 +8102,14 @@
       <c r="AG89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,89 +8143,91 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-16100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-23900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-16700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-45000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-11300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-13400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-16500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-13100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-8700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-6300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-14300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-11300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-12200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-21300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-6100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-6600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-6400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-17300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7799,8 +8240,14 @@
       <c r="AG91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,89 +8442,95 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-349400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-604500</v>
+      </c>
+      <c r="F94" s="3">
         <v>419200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>248200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-299300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-56000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>224900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-267100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>384100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-151200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>522600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>570900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>101000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-362200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-64800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-146900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-196400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-189800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>36200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>171100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>36000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-264100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-3161600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-433600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-269400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-172000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8084,8 +8543,14 @@
       <c r="AG94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8160,11 +8627,11 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,89 +8984,95 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-117100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-371500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-325300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-362000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-134000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-564100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-120100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1017600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-490500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-633500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-88600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-459700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-82200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-223700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-40100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-18300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-22400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-11800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>35500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>50400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>24500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>67800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>22300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>4254400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>9100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>489500</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8594,76 +9085,82 @@
       <c r="AG100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>2600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>8500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-5100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>8500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-2300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-5100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>16</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>16</v>
@@ -8677,11 +9174,11 @@
       <c r="AC101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
+      <c r="AD101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -8689,89 +9186,95 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-377000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-735600</v>
+      </c>
+      <c r="F102" s="3">
         <v>879700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>23800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-358600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-379300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>532400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>853000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-35900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-431800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>781100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>226500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>102500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-285900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>120900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-87900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-156700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-22100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>150300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>236800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>54600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-174400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3119700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3801000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-299000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>310900</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8782,6 +9285,12 @@
         <v>16</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
